--- a/data/valuebets_database_2025-08-20.xlsx
+++ b/data/valuebets_database_2025-08-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>24/08 21:30</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>60</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45889.07250113739</v>
+        <v>45889.07250113426</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>20/08 16:30</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>30.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>30</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45889.07250113739</v>
+        <v>45889.07250113426</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>20/08 19:00</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="F4" t="n">
+        <v>2.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45889.07250113739</v>
+        <v>45889.07250113426</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>22/08 18:45</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>45</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45889.07250113739</v>
+        <v>45889.07250113426</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>23/08 18:30</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>60</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45889.07250113739</v>
+        <v>45889.07250113426</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>23/08 18:30</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>60</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45889.07250113739</v>
+        <v>45889.07250113426</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>20/08 19:00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
+      <c r="F8" t="n">
+        <v>3.7</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45889.07250113739</v>
+        <v>45889.07250113426</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>24/08 18:30</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>60</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45889.07250113739</v>
+        <v>45889.07250113426</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>25/08 20:00</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>55</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45889.07250113739</v>
+        <v>45889.07250113426</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>22/08 00:30</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>55</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45889.07250113739</v>
+        <v>45889.07250113426</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>23/08 11:35</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>55</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45889.07250113739</v>
+        <v>45889.07250113426</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>22/08 18:45</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="F13" t="n">
+        <v>2.5</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45889.07250113739</v>
+        <v>45889.07250113426</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>23/08 18:30</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>50</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45889.07250113739</v>
+        <v>45889.07250113426</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>20/08 19:00</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>16.50</t>
-        </is>
+      <c r="F15" t="n">
+        <v>16.5</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45889.07250113739</v>
+        <v>45889.07250113426</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>25/08 22:00</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>50</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45889.07250113739</v>
+        <v>45889.07250113426</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>21/08 03:00</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
+      <c r="F17" t="n">
+        <v>3.8</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45889.07250113739</v>
+        <v>45889.07250113426</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>24/08 15:30</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>55</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45889.07250113739</v>
+        <v>45889.07250113426</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>22/08 18:45</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>40</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45889.07250113739</v>
+        <v>45889.07250113426</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>27/08 18:45</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>60</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45889.07250113739</v>
+        <v>45889.07250113426</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>20/08 02:10</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>11.50</t>
-        </is>
+      <c r="F21" t="n">
+        <v>11.5</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45889.07250113739</v>
+        <v>45889.07250113426</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>20/08 16:00</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
+      <c r="F22" t="n">
+        <v>3.75</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45889.07250113739</v>
+        <v>45889.07250113426</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>24/08 14:30</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>55</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45889.07250113739</v>
+        <v>45889.07250113426</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>24/08 12:00</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>55</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45889.07250113739</v>
+        <v>45889.07250113426</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>23/08 19:00</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>40</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45889.07250113739</v>
+        <v>45889.07250113426</v>
       </c>
     </row>
     <row r="26">
@@ -1585,23 +1537,291 @@
           <t>23/08 17:00</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" t="n">
+        <v>50</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>+5,75%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>45889.07250113426</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Pumas Unam</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Pumas Unam – Club PueblaLiga MX</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>24/08 23:00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+23,7%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45889.13214213865</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | FC Botosan</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>FC Botosani – FK Csikszereda Miercurea CiucLiga 1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>23/08 15:45</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>50.00</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>+5,75%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>45889.07250113739</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+11,5%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45889.13214213865</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | H 1 (0)1re période | Zhejiang P</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Zhejiang Professional – Tianjin TigersChine - Super League</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>H 1 (0)1re période</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>20/08 11:35</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>66,1%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+3,04%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45889.13214213865</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Basketball | H 1 (+9.5)P | Panama – P</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Panama – Porto-RicoInternational - Americup</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>H 1 (+9.5)P</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>22/08 19:10</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>34,2%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+2,68%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45889.13214213865</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Plus que 6.5 - tir cadré1re équipe | Bodø/Glimt</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Bodø/Glimt – Sturm GrazEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Plus que 6.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>20/08 19:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>34,1%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+2,38%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45889.13214213865</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 21-2- se qualifie | River Plat</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>River Plate (ARG) – Libertad AsuncionInternational. Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>21-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>22/08 00:30</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>15,7%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+2,19%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45889.13214213865</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-20.xlsx
+++ b/data/valuebets_database_2025-08-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>24/08 23:00</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>55</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45889.13214213865</v>
+        <v>45889.13214214121</v>
       </c>
     </row>
     <row r="28">
@@ -1625,10 +1623,8 @@
           <t>23/08 15:45</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>50</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1641,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45889.13214213865</v>
+        <v>45889.13214214121</v>
       </c>
     </row>
     <row r="29">
@@ -1670,10 +1666,8 @@
           <t>20/08 11:35</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
+      <c r="F29" t="n">
+        <v>1.56</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1686,7 +1680,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45889.13214213865</v>
+        <v>45889.13214214121</v>
       </c>
     </row>
     <row r="30">
@@ -1715,10 +1709,8 @@
           <t>22/08 19:10</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F30" t="n">
+        <v>3</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1731,7 +1723,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45889.13214213865</v>
+        <v>45889.13214214121</v>
       </c>
     </row>
     <row r="31">
@@ -1760,10 +1752,8 @@
           <t>20/08 19:00</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>3</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1776,7 +1766,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45889.13214213865</v>
+        <v>45889.13214214121</v>
       </c>
     </row>
     <row r="32">
@@ -1805,10 +1795,8 @@
           <t>22/08 00:30</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
+      <c r="F32" t="n">
+        <v>6.5</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1821,7 +1809,187 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45889.13214213865</v>
+        <v>45889.13214214121</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | 2 | Sky Blue F</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Sky Blue FC (W) – Monterrey (W)International - CONCACAF Champions Cup, Women</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>20/08 23:00</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>26.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>5,02%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+30,6%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45889.18514262329</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Austria Vi</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Austria Vienne – TSV HartbergBundesliga</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>24/08 15:00</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+3,75%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45889.18514262329</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winamax(FR)Football | Plus que 4.5 - tir cadré1re équipe | FC Bâle – </t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>FC Bâle – CopenhagueEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Plus que 4.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>20/08 19:00</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>54,5%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+3,62%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45889.18514262329</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Machida Ze</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Machida Zelvia – Gamba OsakaJ-League</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>20/08 10:00</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+3,27%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45889.18514262329</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-20.xlsx
+++ b/data/valuebets_database_2025-08-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1838,10 +1838,8 @@
           <t>20/08 23:00</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>26.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>26</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1854,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45889.18514262329</v>
+        <v>45889.18514262731</v>
       </c>
     </row>
     <row r="34">
@@ -1883,10 +1881,8 @@
           <t>24/08 15:00</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F34" t="n">
+        <v>45</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1899,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45889.18514262329</v>
+        <v>45889.18514262731</v>
       </c>
     </row>
     <row r="35">
@@ -1928,10 +1924,8 @@
           <t>20/08 19:00</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
+      <c r="F35" t="n">
+        <v>1.9</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1944,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45889.18514262329</v>
+        <v>45889.18514262731</v>
       </c>
     </row>
     <row r="36">
@@ -1973,10 +1967,8 @@
           <t>20/08 10:00</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F36" t="n">
+        <v>45</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1989,7 +1981,187 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45889.18514262329</v>
+        <v>45889.18514262731</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Siauliai –</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Siauliai – Kauno Zalgiris385076e7 A Lyga</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>20/08 16:00</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+5,53%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45889.22344159512</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winamax(FR)Football | Moins que 11re période | Onsala BK </t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Onsala BK – MjallbySweden - Svenska Cupen</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Moins que 11re période</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>20/08 15:30</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>26,2%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+4,80%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45889.22344159512</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Spezia – C</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Spezia – CarrareseSerie B</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>24/08 17:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+3,76%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45889.22344159512</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winamax(FR)Football | Plus que 24.5 - tirs | FC Bâle – </t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>FC Bâle – CopenhagueEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Plus que 24.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>20/08 19:00</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>62,8%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+3,57%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45889.22344159512</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-20.xlsx
+++ b/data/valuebets_database_2025-08-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2010,10 +2010,8 @@
           <t>20/08 16:00</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F37" t="n">
+        <v>40</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2026,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45889.22344159512</v>
+        <v>45889.22344159722</v>
       </c>
     </row>
     <row r="38">
@@ -2055,10 +2053,8 @@
           <t>20/08 15:30</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="F38" t="n">
+        <v>4</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2071,7 +2067,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45889.22344159512</v>
+        <v>45889.22344159722</v>
       </c>
     </row>
     <row r="39">
@@ -2100,10 +2096,8 @@
           <t>24/08 17:00</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F39" t="n">
+        <v>50</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2116,7 +2110,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45889.22344159512</v>
+        <v>45889.22344159722</v>
       </c>
     </row>
     <row r="40">
@@ -2145,10 +2139,8 @@
           <t>20/08 19:00</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
+      <c r="F40" t="n">
+        <v>1.65</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2161,7 +2153,232 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45889.22344159512</v>
+        <v>45889.22344159722</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.52e équipe | Celtic – K</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Celtic – Kairat AlmatyLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>20/08 19:00</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+22,3%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45889.27333494955</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 14.5 - tirs2e équipe | Fenerbahce</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Fenerbahce – BenficaLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Plus que 14.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>20/08 19:00</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>37,6%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+20,4%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45889.27333494955</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winamax(FR)Football | Plus que 27.5 - tirs | FC Bâle – </t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>FC Bâle – CopenhagueEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Plus que 27.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>20/08 19:00</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>42,8%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+15,5%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45889.27333494955</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | CD Univers</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica – Alianza LimaCopa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>21/08 00:30</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+5,13%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45889.27333494955</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 6.5 - tir cadré | Betis – Al</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Betis – AlavesEspagne - Espagne LaLiga</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Moins que 6.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>22/08 19:30</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>33,4%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+3,49%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45889.27333494955</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-20.xlsx
+++ b/data/valuebets_database_2025-08-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2182,10 +2182,8 @@
           <t>20/08 19:00</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F41" t="n">
+        <v>50</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2198,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45889.27333494955</v>
+        <v>45889.2733349537</v>
       </c>
     </row>
     <row r="42">
@@ -2227,10 +2225,8 @@
           <t>20/08 19:00</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="F42" t="n">
+        <v>3.2</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2243,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45889.27333494955</v>
+        <v>45889.2733349537</v>
       </c>
     </row>
     <row r="43">
@@ -2272,10 +2268,8 @@
           <t>20/08 19:00</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F43" t="n">
+        <v>2.7</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2288,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45889.27333494955</v>
+        <v>45889.2733349537</v>
       </c>
     </row>
     <row r="44">
@@ -2317,10 +2311,8 @@
           <t>21/08 00:30</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F44" t="n">
+        <v>45</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2333,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45889.27333494955</v>
+        <v>45889.2733349537</v>
       </c>
     </row>
     <row r="45">
@@ -2362,10 +2354,8 @@
           <t>22/08 19:30</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="F45" t="n">
+        <v>3.1</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2378,7 +2368,232 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45889.27333494955</v>
+        <v>45889.2733349537</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 4.5 - tir cadré2e équipe | CA Indepen</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CA Independiente – Universidad de ChileInternational - Copa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Plus que 4.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>21/08 00:30</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>36,3%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+63,3%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45889.30664583149</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 26.5 - tirs | Bayern Mun</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Bayern Munich – RB LeipzigAllemagne - Allemagne Bundesliga</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Moins que 26.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>22/08 18:30</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>40,9%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+35,0%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45889.30664583149</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 14.5 - tirs2e équipe | Fenerbahçe</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Fenerbahçe – BenficaEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Plus que 14.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>20/08 19:00</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>37,4%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+23,3%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45889.30664583149</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 11.5 - tirs2e équipe | Universida</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Universidad Catolica del Ecuador – Alianza LimaInternational - Copa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Plus que 11.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>21/08 00:30</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>39,0%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+13,0%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45889.30664583149</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PMU(FR)Tennis | 21-2 | Crawford, </t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>PMU(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Crawford, Oliver – Johns, GarrettEvénements. US Open (QH)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>21-2</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>20/08 21:00</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>42,4%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+8,16%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45889.30664583149</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-20.xlsx
+++ b/data/valuebets_database_2025-08-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2397,10 +2397,8 @@
           <t>21/08 00:30</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="F46" t="n">
+        <v>4.5</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2413,7 +2411,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45889.30664583149</v>
+        <v>45889.30664583333</v>
       </c>
     </row>
     <row r="47">
@@ -2442,10 +2440,8 @@
           <t>22/08 18:30</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="F47" t="n">
+        <v>3.3</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2458,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45889.30664583149</v>
+        <v>45889.30664583333</v>
       </c>
     </row>
     <row r="48">
@@ -2487,10 +2483,8 @@
           <t>20/08 19:00</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="F48" t="n">
+        <v>3.3</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2503,7 +2497,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45889.30664583149</v>
+        <v>45889.30664583333</v>
       </c>
     </row>
     <row r="49">
@@ -2532,10 +2526,8 @@
           <t>21/08 00:30</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="F49" t="n">
+        <v>2.9</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2548,7 +2540,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45889.30664583149</v>
+        <v>45889.30664583333</v>
       </c>
     </row>
     <row r="50">
@@ -2577,10 +2569,8 @@
           <t>20/08 21:00</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
+      <c r="F50" t="n">
+        <v>2.55</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2593,7 +2583,97 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45889.30664583149</v>
+        <v>45889.30664583333</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | Moins que 4.5 - break1er participant | Marie Bouz</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Marie Bouzkova – Beatriz Haddad MaiaWTA - Monterrey</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Moins que 4.5 - break1er participant</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>20/08 23:00</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>60,9%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+21,7%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45889.35371431687</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Plus que 6.5 - tir cadré1re équipe | Fenerbahce</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Fenerbahce – BenficaEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Plus que 6.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>20/08 19:00</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>28,5%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+5,45%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45889.35371431687</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-20.xlsx
+++ b/data/valuebets_database_2025-08-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2612,10 +2612,8 @@
           <t>20/08 23:00</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="F51" t="n">
+        <v>2</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2628,7 +2626,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45889.35371431687</v>
+        <v>45889.35371431713</v>
       </c>
     </row>
     <row r="52">
@@ -2657,23 +2655,66 @@
           <t>20/08 19:00</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F52" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>28,5%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+5,45%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45889.35371431713</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winamax(FR)Basketball | H 1 (+16.5)P | Denmark – </t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Denmark – CroatiaInternational - World Cup, Qualifying</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>H 1 (+16.5)P</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>20/08 17:00</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>3.70</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>28,5%</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>+5,45%</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="n">
-        <v>45889.35371431687</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>30,7%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+13,4%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45889.39198263038</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-20.xlsx
+++ b/data/valuebets_database_2025-08-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2698,10 +2698,8 @@
           <t>20/08 17:00</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
+      <c r="F53" t="n">
+        <v>3.7</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2714,7 +2712,52 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45889.39198263038</v>
+        <v>45889.39198262731</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>PMU(FR)Tennis | Moins que 8.51er set | Vekic, Don</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>PMU(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Vekic, Donna – Mertens, EliseEvénements. WTA Monterrey</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Moins que 8.51er set</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>20/08 21:00</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>29,3%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+5,33%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45889.43327896355</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-20.xlsx
+++ b/data/valuebets_database_2025-08-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2741,10 +2741,8 @@
           <t>20/08 21:00</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
+      <c r="F54" t="n">
+        <v>3.6</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2757,7 +2755,232 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45889.43327896355</v>
+        <v>45889.43327895833</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 1 - aces | R.Sramkova</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>R.Sramkova – L.FernandezWTA - Monterrey</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>20/08 22:10</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>55,1%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+23,9%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45889.4713585264</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 1 - aces | G.Diallo –</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>G.Diallo – H.MedjedovicATP - Winston Salem</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>20/08 20:00</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>74,0%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+14,7%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45889.4713585264</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | X2 | FK Liepaja</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>FK Liepaja – SK Super NovaLettonie - Virsliga</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>25/08 14:30</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>38,0%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+14,0%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45889.4713585264</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 5.5 | Deportivo </t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Deportivo Riestra – CA SarmientoLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Plus que 5.5</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>25/08 18:00</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+6,74%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45889.4713585264</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 5.5 | Union Sant</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Union Santa Fe – CA HuracanLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Plus que 5.5</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>24/08 17:00</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+5,91%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45889.4713585264</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-20.xlsx
+++ b/data/valuebets_database_2025-08-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2784,10 +2784,8 @@
           <t>20/08 22:10</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
+      <c r="F55" t="n">
+        <v>2.25</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2800,7 +2798,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45889.4713585264</v>
+        <v>45889.47135853009</v>
       </c>
     </row>
     <row r="56">
@@ -2829,10 +2827,8 @@
           <t>20/08 20:00</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
+      <c r="F56" t="n">
+        <v>1.55</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2845,7 +2841,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45889.4713585264</v>
+        <v>45889.47135853009</v>
       </c>
     </row>
     <row r="57">
@@ -2874,10 +2870,8 @@
           <t>25/08 14:30</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F57" t="n">
+        <v>3</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2890,7 +2884,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45889.4713585264</v>
+        <v>45889.47135853009</v>
       </c>
     </row>
     <row r="58">
@@ -2919,10 +2913,8 @@
           <t>25/08 18:00</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F58" t="n">
+        <v>50</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2935,7 +2927,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45889.4713585264</v>
+        <v>45889.47135853009</v>
       </c>
     </row>
     <row r="59">
@@ -2964,10 +2956,8 @@
           <t>24/08 17:00</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F59" t="n">
+        <v>55</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2980,7 +2970,277 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45889.4713585264</v>
+        <v>45889.47135853009</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Moins que 23.5 - tirs | Bodø/Glimt</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Bodø/Glimt – Sturm GrazEurope - Ligue des Champions stq pr cu 385076e7</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Moins que 23.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>20/08 19:00</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>35,7%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+16,1%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45889.53098033502</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Plus que 3 | FK Sloboda</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>FK Sloboda Novi Grad – Velez NevesinjeBosnia &amp; Herzegovina - Prva Liga, Republic of Srpska</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Plus que 3</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>21/08 15:00</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>29,6%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+15,4%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45889.53098033502</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Tennis | Moins que 3.51er set1er participant | Sebastian </t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Sebastian Baez – Botic Van de ZandschulpATP 250 Winston Salem</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Moins que 3.51er set1er participant</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>20/08 23:40</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>36,5%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+9,37%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45889.53098033502</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Basketball | H 1 (−17.5)P | SC Corinth</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>SC Corinthians Paulista – Rio Claro Basquete SPBrazil - Campeonat Paulista</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>H 1 (−17.5)P</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>20/08 23:30</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>46,2%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+8,49%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45889.53098033502</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | La Corogne</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>La Corogne – Burgos CFLaLiga2</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>24/08 15:00</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+7,65%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45889.53098033502</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | 2 / DNB | Flint Town</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Flint Town United FC – Cearnarfon TownPays de Galles - Cymru Premier League</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2 / DNB</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>22/08 18:45</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>65,4%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+7,19%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45889.53098033502</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-20.xlsx
+++ b/data/valuebets_database_2025-08-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2999,10 +2999,8 @@
           <t>20/08 19:00</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
+      <c r="F60" t="n">
+        <v>3.25</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3015,7 +3013,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45889.53098033502</v>
+        <v>45889.53098033565</v>
       </c>
     </row>
     <row r="61">
@@ -3044,10 +3042,8 @@
           <t>21/08 15:00</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
+      <c r="F61" t="n">
+        <v>3.9</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3060,7 +3056,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45889.53098033502</v>
+        <v>45889.53098033565</v>
       </c>
     </row>
     <row r="62">
@@ -3089,10 +3085,8 @@
           <t>20/08 23:40</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F62" t="n">
+        <v>3</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3105,7 +3099,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45889.53098033502</v>
+        <v>45889.53098033565</v>
       </c>
     </row>
     <row r="63">
@@ -3134,10 +3128,8 @@
           <t>20/08 23:30</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
+      <c r="F63" t="n">
+        <v>2.35</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3150,7 +3142,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45889.53098033502</v>
+        <v>45889.53098033565</v>
       </c>
     </row>
     <row r="64">
@@ -3179,10 +3171,8 @@
           <t>24/08 15:00</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F64" t="n">
+        <v>50</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3195,7 +3185,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45889.53098033502</v>
+        <v>45889.53098033565</v>
       </c>
     </row>
     <row r="65">
@@ -3224,10 +3214,8 @@
           <t>22/08 18:45</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
+      <c r="F65" t="n">
+        <v>1.64</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3240,7 +3228,97 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45889.53098033502</v>
+        <v>45889.53098033565</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Moins que 13.5 - tirs1re équipe | Bodø/Glimt</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Bodø/Glimt – Sturm GrazEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Moins que 13.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>20/08 19:00</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>34,4%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+11,9%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45889.56407094079</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winamax(FR)Basketball | H 2 (+3.5)P | Finland – </t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Finland – PolandInternational - International Friendly Games (M)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>H 2 (+3.5)P</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>21/08 15:30</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>4.60</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>23,2%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>+6,56%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45889.56407094079</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-20.xlsx
+++ b/data/valuebets_database_2025-08-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3257,10 +3257,8 @@
           <t>20/08 19:00</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
+      <c r="F66" t="n">
+        <v>3.25</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3273,7 +3271,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45889.56407094079</v>
+        <v>45889.5640709375</v>
       </c>
     </row>
     <row r="67">
@@ -3302,10 +3300,8 @@
           <t>21/08 15:30</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>4.60</t>
-        </is>
+      <c r="F67" t="n">
+        <v>4.6</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3318,7 +3314,52 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>45889.56407094079</v>
+        <v>45889.5640709375</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winamax(FR)Handball | 1X | HC Kyndil </t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Handball</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>HC Kyndil Torshavn – RK Nexe NasiceInternational - Club Friendly Games</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>20/08 14:30</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>5,16%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>+18,7%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>45889.59968905283</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-20.xlsx
+++ b/data/valuebets_database_2025-08-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3343,10 +3343,8 @@
           <t>20/08 14:30</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>23.00</t>
-        </is>
+      <c r="F68" t="n">
+        <v>23</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3359,7 +3357,97 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>45889.59968905283</v>
+        <v>45889.59968905093</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.52e équipe | Breidablik</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Breidablik – SS VirtusLigue Europa Conférence</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>21/08 18:00</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>+34,3%</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>45889.64189074463</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | 2 / DNB | FK Liepaja</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>FK Liepaja – SK Super NovaLettonie - Virsliga</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2 / DNB</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>25/08 14:30</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>19,4%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>+26,2%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>45889.64189074463</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-20.xlsx
+++ b/data/valuebets_database_2025-08-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3386,10 +3386,8 @@
           <t>21/08 18:00</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F69" t="n">
+        <v>60</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3402,7 +3400,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>45889.64189074463</v>
+        <v>45889.64189074074</v>
       </c>
     </row>
     <row r="70">
@@ -3431,10 +3429,8 @@
           <t>25/08 14:30</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
+      <c r="F70" t="n">
+        <v>6.5</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3447,7 +3443,232 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>45889.64189074463</v>
+        <v>45889.64189074074</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Plus que 2.52e équipe | FK Liepaja</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>FK Liepaja – SK Super NovaLettonie - Virsliga</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>25/08 14:30</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>21.00</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>6,05%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>+27,0%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>45889.68569129816</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 30.5 - tirs | Bayern Mun</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Bayern Munich – RB LeipzigAllemagne - Allemagne Bundesliga</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Moins que 30.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>22/08 18:30</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>67,1%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>+15,4%</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>45889.68569129816</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | 11-2- se qualifie | Qviding Fi</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Qviding Fif – IFK GöteborgSweden - Svenska Cupen</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>11-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>20/08 16:30</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>30.00</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>3,60%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>+7,99%</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>45889.68569129816</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Moins que 2 | FC Stockho</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>FC Stockholm Internazionale – IF BrommapojkarnaSweden - Svenska Cupen</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Moins que 2</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>21/08 16:30</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>32,0%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>+5,73%</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>45889.68569129816</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>PMU(FR)Basketball | X(17:0)P | Grande-Bre</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>PMU(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Grande-Bretagne – LituanieBasket FIBA. EuroBasket</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>X(17:0)P</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>27/08 10:30</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>5,54%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>+5,18%</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>45889.68569129816</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-20.xlsx
+++ b/data/valuebets_database_2025-08-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3472,10 +3472,8 @@
           <t>25/08 14:30</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>21.00</t>
-        </is>
+      <c r="F71" t="n">
+        <v>21</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3488,7 +3486,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>45889.68569129816</v>
+        <v>45889.6856912963</v>
       </c>
     </row>
     <row r="72">
@@ -3517,10 +3515,8 @@
           <t>22/08 18:30</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
+      <c r="F72" t="n">
+        <v>1.72</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3533,7 +3529,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>45889.68569129816</v>
+        <v>45889.6856912963</v>
       </c>
     </row>
     <row r="73">
@@ -3562,10 +3558,8 @@
           <t>20/08 16:30</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>30.00</t>
-        </is>
+      <c r="F73" t="n">
+        <v>30</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3578,7 +3572,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>45889.68569129816</v>
+        <v>45889.6856912963</v>
       </c>
     </row>
     <row r="74">
@@ -3607,10 +3601,8 @@
           <t>21/08 16:30</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="F74" t="n">
+        <v>3.3</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3623,7 +3615,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45889.68569129816</v>
+        <v>45889.6856912963</v>
       </c>
     </row>
     <row r="75">
@@ -3652,10 +3644,8 @@
           <t>27/08 10:30</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>19.00</t>
-        </is>
+      <c r="F75" t="n">
+        <v>19</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3668,7 +3658,52 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>45889.68569129816</v>
+        <v>45889.6856912963</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Pas de corners | Toluca – O</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Toluca – Orlando City SCInternational - Leagues Cup</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Pas de corners</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>21/08 00:50</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>+5,44%</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>45889.72184077324</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-20.xlsx
+++ b/data/valuebets_database_2025-08-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3687,10 +3687,8 @@
           <t>21/08 00:50</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F76" t="n">
+        <v>100</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3703,7 +3701,142 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>45889.72184077324</v>
+        <v>45889.72184077546</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Barry Town</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Barry Town – PenybontCymru Premier</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>22/08 18:45</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>+46,4%</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>45889.77209911952</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 12.5 - tirs2e équipe | Universida</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Universidad Catolica del Ecuador – Alianza LimaInternational - Copa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Plus que 12.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>21/08 00:30</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>38,0%</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>+6,38%</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>45889.77209911952</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | EC Bahia –</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>EC Bahia – SantosSérie A</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>24/08 19:00</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>+6,08%</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>45889.77209911952</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-20.xlsx
+++ b/data/valuebets_database_2025-08-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3730,10 +3730,8 @@
           <t>22/08 18:45</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F77" t="n">
+        <v>55</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3746,7 +3744,7 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>45889.77209911952</v>
+        <v>45889.77209912037</v>
       </c>
     </row>
     <row r="78">
@@ -3775,10 +3773,8 @@
           <t>21/08 00:30</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="F78" t="n">
+        <v>2.8</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3791,7 +3787,7 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>45889.77209911952</v>
+        <v>45889.77209912037</v>
       </c>
     </row>
     <row r="79">
@@ -3820,10 +3816,8 @@
           <t>24/08 19:00</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F79" t="n">
+        <v>55</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3836,7 +3830,187 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>45889.77209911952</v>
+        <v>45889.77209912037</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.52e équipe | Rakow Czes</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Rakow Czestochowa – Arda KardzhaliLigue Europa Conférence</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>21/08 19:00</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>+14,3%</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>45889.80389764435</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Pas de corners | Inter Miam</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Inter Miami CF – TigresInternational - Leagues Cup</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Pas de corners</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>21/08 00:00</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>+5,44%</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>45889.80389764435</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | 1 / DNB | FK Riteria</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>FK Riteriai – DžiugasLituanie - A Lyga</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1 / DNB</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>22/08 16:00</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>38,2%</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>+4,99%</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>45889.80389764435</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Remplaçant marque un but: Oui | Atletico M</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Atletico Madrid – ElcheLaLiga</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Remplaçant marque un but: Oui</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>23/08 17:30</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>41,9%</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>+4,67%</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>45889.80389764435</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-20.xlsx
+++ b/data/valuebets_database_2025-08-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3859,10 +3859,8 @@
           <t>21/08 19:00</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F80" t="n">
+        <v>50</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3875,7 +3873,7 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>45889.80389764435</v>
+        <v>45889.80389763889</v>
       </c>
     </row>
     <row r="81">
@@ -3904,10 +3902,8 @@
           <t>21/08 00:00</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F81" t="n">
+        <v>100</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3920,7 +3916,7 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>45889.80389764435</v>
+        <v>45889.80389763889</v>
       </c>
     </row>
     <row r="82">
@@ -3949,10 +3945,8 @@
           <t>22/08 16:00</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F82" t="n">
+        <v>2.75</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3965,7 +3959,7 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>45889.80389764435</v>
+        <v>45889.80389763889</v>
       </c>
     </row>
     <row r="83">
@@ -3994,23 +3988,246 @@
           <t>23/08 17:30</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="F83" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>41,9%</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>+4,67%</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>45889.80389763889</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.52e équipe | Crystal Pa</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Crystal Palace – FredrikstadLigue Europa Conférence</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>21/08 19:00</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>+24,7%</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>45889.85025894191</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Remplaçant marque un but: Oui | Levante – </t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Levante – FC BarceloneLaLiga</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Remplaçant marque un but: Oui</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>23/08 19:30</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
         <is>
           <t>2.50</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>41,9%</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>+4,67%</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="n">
-        <v>45889.80389764435</v>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>44,0%</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>+10,0%</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>45889.85025894191</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>PMU(FR)Basketball | X(12:0)P | Monténégro</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>PMU(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Monténégro – AllemagneBasket FIBA. EuroBasket</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>X(12:0)P</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>27/08 13:30</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>19.75</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>5,44%</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>+7,38%</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>45889.85025894191</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>PMU(FR)Tennis | Moins que 8.51er set | Gabriel Di</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>PMU(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Gabriel Diallo – Medjedovic, HamadEvénements. ATP Winston Salem</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Moins que 8.51er set</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>20/08 20:30</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>14,2%</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>+6,39%</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>45889.85025894191</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 2 | The New Sa</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>The New Saints – Connahs QuayPays de Galles. Pays de Galles - Premiership</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>22/08 18:45</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>8,14%</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>+5,87%</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>45889.85025894191</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-20.xlsx
+++ b/data/valuebets_database_2025-08-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I88"/>
+  <dimension ref="A1:I89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4031,10 +4031,8 @@
           <t>21/08 19:00</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F84" t="n">
+        <v>60</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -4047,7 +4045,7 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>45889.85025894191</v>
+        <v>45889.85025894676</v>
       </c>
     </row>
     <row r="85">
@@ -4076,10 +4074,8 @@
           <t>23/08 19:30</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="F85" t="n">
+        <v>2.5</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -4092,7 +4088,7 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>45889.85025894191</v>
+        <v>45889.85025894676</v>
       </c>
     </row>
     <row r="86">
@@ -4121,10 +4117,8 @@
           <t>27/08 13:30</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>19.75</t>
-        </is>
+      <c r="F86" t="n">
+        <v>19.75</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -4137,7 +4131,7 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>45889.85025894191</v>
+        <v>45889.85025894676</v>
       </c>
     </row>
     <row r="87">
@@ -4166,10 +4160,8 @@
           <t>20/08 20:30</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
+      <c r="F87" t="n">
+        <v>7.5</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -4182,7 +4174,7 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>45889.85025894191</v>
+        <v>45889.85025894676</v>
       </c>
     </row>
     <row r="88">
@@ -4211,10 +4203,8 @@
           <t>22/08 18:45</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>13.00</t>
-        </is>
+      <c r="F88" t="n">
+        <v>13</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -4227,7 +4217,52 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>45889.85025894191</v>
+        <v>45889.85025894676</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winamax(FR)Basketball | H 2 (+8.5)P | Finland – </t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Finland – PolandInternational - International Friendly Games (M)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>H 2 (+8.5)P</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>21/08 15:30</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>45,3%</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>+15,5%</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>45889.88916976019</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-20.xlsx
+++ b/data/valuebets_database_2025-08-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I89"/>
+  <dimension ref="A1:I91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4246,10 +4246,8 @@
           <t>21/08 15:30</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
+      <c r="F89" t="n">
+        <v>2.55</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -4262,7 +4260,97 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>45889.88916976019</v>
+        <v>45889.88916975694</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Futsal | Pas de buts | AD Indaiat</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Futsal</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>AD Indaiatuba – Corinthians Sao Paulo SPBrazil - Campeonato Paulista</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>20/08 22:30</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>+101%</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>45889.93023369089</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | EC Juventu</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>EC Juventude – BotafogoSérie A</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>24/08 21:30</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>+20,7%</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>45889.93023369089</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-20.xlsx
+++ b/data/valuebets_database_2025-08-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I91"/>
+  <dimension ref="A1:I94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4289,10 +4289,8 @@
           <t>20/08 22:30</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F90" t="n">
+        <v>100</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -4305,7 +4303,7 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>45889.93023369089</v>
+        <v>45889.93023369213</v>
       </c>
     </row>
     <row r="91">
@@ -4334,23 +4332,156 @@
           <t>24/08 21:30</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="F91" t="n">
+        <v>60</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>+20,7%</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>45889.93023369213</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Leon – Que</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Leon – Queretaro FCLiga MX</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>30/08 23:00</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
         <is>
           <t>60.00</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>+20,7%</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="n">
-        <v>45889.93023369089</v>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>+22,8%</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>45889.97204111589</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | H 1 (−1.5) | Real Carta</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Real Cartagena – TigresColombia - Primera B, Clausura</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>H 1 (−1.5)</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>22/08 23:00</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>38,8%</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>+6,70%</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>45889.97204111589</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 21-2- se qualifie | Wolfsberge</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Wolfsberger AC – Omonia NicosieEurope. Europa Conférence (Q)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>21-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>21/08 17:00</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>50,7%</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>+6,41%</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>45889.97204111589</v>
       </c>
     </row>
   </sheetData>
